--- a/VerveStacks_EST/vt_vervestacks_EST_v1.xlsx
+++ b/VerveStacks_EST/vt_vervestacks_EST_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F31F53A6-131B-4BA5-B745-517804E24EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E424703-8A53-48D2-9A99-C4FAB6BB0300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{92740B63-BC80-4AF4-A078-447101E0683B}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -829,7 +829,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C047CB67-FC18-43CA-8AA0-0CA09A11D4D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58229956-3CA7-477D-89D1-002D9B663EC9}">
   <dimension ref="B9:T15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1183,7 +1183,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41A4FEF-80F2-457D-B441-6C3DD45005FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1021D03-37B0-4402-9FDC-33426C143D44}">
   <dimension ref="B9:T28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1383,7 +1383,7 @@
         <v>121.00000000000003</v>
       </c>
       <c r="J13">
-        <v>3.4650000000000007</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>30</v>
@@ -1439,7 +1439,7 @@
         <v>110.00000000000001</v>
       </c>
       <c r="J14">
-        <v>3.1500000000000004</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>30</v>
@@ -1495,7 +1495,7 @@
         <v>110.00000000000001</v>
       </c>
       <c r="J15">
-        <v>3.1500000000000008</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>30</v>
@@ -1551,7 +1551,7 @@
         <v>110.00000000000001</v>
       </c>
       <c r="J16">
-        <v>3.1500000000000004</v>
+        <v>0</v>
       </c>
       <c r="K16">
         <v>30</v>
@@ -1607,7 +1607,7 @@
         <v>110.00000000000003</v>
       </c>
       <c r="J17">
-        <v>3.1500000000000004</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <v>30</v>
@@ -1663,7 +1663,7 @@
         <v>110.00000000000001</v>
       </c>
       <c r="J18">
-        <v>3.1500000000000004</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>30</v>
@@ -1719,7 +1719,7 @@
         <v>110.00000000000001</v>
       </c>
       <c r="J19">
-        <v>3.1500000000000004</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>30</v>
@@ -1931,7 +1931,7 @@
         <v>110.00000000000001</v>
       </c>
       <c r="J23">
-        <v>3.1500000000000008</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <v>30</v>
@@ -1987,7 +1987,7 @@
         <v>110.00000000000001</v>
       </c>
       <c r="J24">
-        <v>3.1500000000000004</v>
+        <v>0</v>
       </c>
       <c r="K24">
         <v>30</v>
@@ -2043,7 +2043,7 @@
         <v>110.00000000000001</v>
       </c>
       <c r="J25">
-        <v>3.1500000000000004</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>30</v>
@@ -2099,7 +2099,7 @@
         <v>110.00000000000001</v>
       </c>
       <c r="J26">
-        <v>3.1500000000000004</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>30</v>
@@ -2155,7 +2155,7 @@
         <v>110.00000000000003</v>
       </c>
       <c r="J27">
-        <v>3.1500000000000004</v>
+        <v>0</v>
       </c>
       <c r="K27">
         <v>30</v>
@@ -2211,7 +2211,7 @@
         <v>110.00000000000001</v>
       </c>
       <c r="J28">
-        <v>3.1500000000000004</v>
+        <v>0</v>
       </c>
       <c r="K28">
         <v>30</v>
@@ -2247,7 +2247,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A97F7A1B-74BD-44D2-B5BC-9103C418FE5E}">
   <dimension ref="B9:T47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3380,7 +3380,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L31">
-        <v>0.42012333946150526</v>
+        <v>0.42012333946150532</v>
       </c>
       <c r="N31" t="s">
         <v>69</v>
@@ -3424,7 +3424,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L32">
-        <v>0.42012333946150526</v>
+        <v>0.42012333946150532</v>
       </c>
       <c r="N32" t="s">
         <v>69</v>
@@ -3468,7 +3468,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L33">
-        <v>0.42012333946150526</v>
+        <v>0.42012333946150532</v>
       </c>
       <c r="N33" t="s">
         <v>69</v>
@@ -3518,7 +3518,7 @@
         <v>57.2</v>
       </c>
       <c r="J34">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="K34">
         <v>46</v>
@@ -3574,7 +3574,7 @@
         <v>57.2</v>
       </c>
       <c r="J35">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="K35">
         <v>45</v>
@@ -3630,7 +3630,7 @@
         <v>57.20000000000001</v>
       </c>
       <c r="J36">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <v>40</v>
@@ -3686,7 +3686,7 @@
         <v>57.20000000000001</v>
       </c>
       <c r="J37">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <v>35</v>
@@ -3721,7 +3721,7 @@
         <v>57.2</v>
       </c>
       <c r="J38">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <v>48</v>
@@ -3756,7 +3756,7 @@
         <v>57.20000000000001</v>
       </c>
       <c r="J39">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="K39">
         <v>44</v>
@@ -3791,7 +3791,7 @@
         <v>57.2</v>
       </c>
       <c r="J40">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="K40">
         <v>43</v>
@@ -3826,7 +3826,7 @@
         <v>57.2</v>
       </c>
       <c r="J41">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="K41">
         <v>32</v>
@@ -3861,7 +3861,7 @@
         <v>48.4</v>
       </c>
       <c r="J42">
-        <v>2.3100000000000005</v>
+        <v>0</v>
       </c>
       <c r="K42">
         <v>31</v>
@@ -3896,7 +3896,7 @@
         <v>57.2</v>
       </c>
       <c r="J43">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="K43">
         <v>32</v>
@@ -3931,7 +3931,7 @@
         <v>57.20000000000001</v>
       </c>
       <c r="J44">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="K44">
         <v>50</v>
@@ -3966,7 +3966,7 @@
         <v>57.2</v>
       </c>
       <c r="J45">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="K45">
         <v>43</v>
@@ -4001,7 +4001,7 @@
         <v>57.2</v>
       </c>
       <c r="J46">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="K46">
         <v>42</v>
@@ -4036,7 +4036,7 @@
         <v>48.400000000000006</v>
       </c>
       <c r="J47">
-        <v>2.3100000000000005</v>
+        <v>0</v>
       </c>
       <c r="K47">
         <v>31</v>
@@ -4051,7 +4051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CEAB3BD-FD82-4128-8F02-FA58B77D374D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C5FD5D-D1AE-4200-BCBA-7FEB103C3BB2}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
